--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487062_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487062_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>E. ERRASTI DIEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.519</v>
+        <v>7.7117</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2583</v>
+        <v>7.2858</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2607</v>
+        <v>0.4259</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7758</v>
+        <v>6.567</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1093</v>
+        <v>1.6766</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3335</v>
+        <v>4.8903</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4756</v>
+        <v>6.6137</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3699</v>
+        <v>2.251</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1057</v>
+        <v>4.3627</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6998</v>
+        <v>-0.0467</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2607</v>
+        <v>-0.5743</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4391</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.386</v>
+        <v>1.158</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="S2" t="n">
-        <v>5.9013</v>
+        <v>-0.3414</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4848</v>
+        <v>0.0582</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4165</v>
+        <v>-0.3996</v>
       </c>
       <c r="V2" t="n">
-        <v>1.228</v>
+        <v>0.3281</v>
       </c>
       <c r="W2" t="n">
-        <v>1.228</v>
+        <v>0.614</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. ERRASTI DIEZ</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.2844</v>
+        <v>5.9997</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8853</v>
+        <v>3.7562</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3991</v>
+        <v>2.2435</v>
       </c>
       <c r="G3" t="n">
-        <v>6.567</v>
+        <v>1.7758</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6766</v>
+        <v>2.1093</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8903</v>
+        <v>-0.3335</v>
       </c>
       <c r="J3" t="n">
-        <v>6.6137</v>
+        <v>2.4756</v>
       </c>
       <c r="K3" t="n">
-        <v>2.251</v>
+        <v>2.3699</v>
       </c>
       <c r="L3" t="n">
-        <v>4.3627</v>
+        <v>0.1057</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0467</v>
+        <v>-0.6998</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5743</v>
+        <v>-0.2607</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.4391</v>
       </c>
       <c r="P3" t="n">
-        <v>1.158</v>
+        <v>-0.386</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>1.158</v>
+        <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7687</v>
+        <v>3.3819</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3424</v>
+        <v>1.9827</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4264</v>
+        <v>1.3993</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3281</v>
+        <v>1.228</v>
       </c>
       <c r="W3" t="n">
-        <v>0.614</v>
+        <v>1.228</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4074</v>
+        <v>3.7669</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2041</v>
+        <v>4.403</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7967</v>
+        <v>-0.6361</v>
       </c>
       <c r="G4" t="n">
         <v>2.0362</v>
@@ -766,13 +766,13 @@
         <v>0.772</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6644</v>
+        <v>1.0239</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8984</v>
+        <v>1.0973</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.234</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0.8999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2377</v>
+        <v>3.4066</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7757</v>
+        <v>2.677</v>
       </c>
       <c r="F5" t="n">
-        <v>0.462</v>
+        <v>0.7297</v>
       </c>
       <c r="G5" t="n">
         <v>0.1959</v>
@@ -844,13 +844,13 @@
         <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>0.119</v>
+        <v>1.2879</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1057</v>
+        <v>0.7955</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2247</v>
+        <v>0.4924</v>
       </c>
       <c r="V5" t="n">
         <v>0.5717</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.606</v>
+        <v>2.4078</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4101</v>
+        <v>0.333</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1959</v>
+        <v>2.0748</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1904</v>
+        <v>0.0509</v>
       </c>
       <c r="H6" t="n">
-        <v>0.707</v>
+        <v>0.4886</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4834</v>
+        <v>-0.4377</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1035</v>
+        <v>-0.3437</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0143</v>
+        <v>0.2018</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0893</v>
+        <v>-0.5455</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0868</v>
+        <v>0.3946</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3073</v>
+        <v>0.2868</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3941</v>
+        <v>0.1078</v>
       </c>
       <c r="P6" t="n">
         <v>0.386</v>
@@ -922,19 +922,19 @@
         <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5843</v>
+        <v>0.4571</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3424</v>
+        <v>0.1279</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2419</v>
+        <v>0.3291</v>
       </c>
       <c r="V6" t="n">
-        <v>0.614</v>
+        <v>1.5138</v>
       </c>
       <c r="W6" t="n">
-        <v>0.614</v>
+        <v>1.5138</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3995</v>
+        <v>1.7528</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5683</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9677</v>
+        <v>1.1424</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0509</v>
+        <v>1.1904</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4886</v>
+        <v>0.707</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4377</v>
+        <v>0.4834</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3437</v>
+        <v>1.1035</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2018</v>
+        <v>1.0143</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5455</v>
+        <v>0.0893</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3946</v>
+        <v>0.0868</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2868</v>
+        <v>-0.3073</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1078</v>
+        <v>0.3941</v>
       </c>
       <c r="P7" t="n">
         <v>0.386</v>
@@ -1000,19 +1000,19 @@
         <v>1.3511</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5513</v>
+        <v>-0.4376</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7733</v>
+        <v>-0.1421</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2221</v>
+        <v>-0.2955</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5138</v>
+        <v>0.614</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5138</v>
+        <v>0.614</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1183</v>
+        <v>0.9984</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5365</v>
+        <v>-0.7368</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6549</v>
+        <v>1.7352</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2168</v>
@@ -1078,13 +1078,13 @@
         <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3002</v>
+        <v>1.1802</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2295</v>
+        <v>1.0292</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0707</v>
+        <v>0.151</v>
       </c>
       <c r="V8" t="n">
         <v>1.228</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. MENDIA SANGRONIZ</t>
+          <t>E. SALINERO GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0653</v>
+        <v>-0.6419</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0303</v>
+        <v>-1.2472</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0956</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4879</v>
+        <v>-0.344</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1615</v>
+        <v>0.0487</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6494</v>
+        <v>-0.3927</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8208</v>
+        <v>0.6228</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4088</v>
+        <v>0.1758</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2295</v>
+        <v>0.447</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6671</v>
+        <v>-0.9669</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2473</v>
+        <v>-0.1272</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4199</v>
+        <v>-0.8397</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.965</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9301</v>
+        <v>-3.8602</v>
       </c>
       <c r="R9" t="n">
-        <v>0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4455</v>
+        <v>1.0761</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3252</v>
+        <v>0.7621</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1203</v>
+        <v>0.3139</v>
       </c>
       <c r="V9" t="n">
         <v>0.9421</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4559</v>
+        <v>1.228</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5138</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. SALINERO GARCIA</t>
+          <t>B. MENDIA SANGRONIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.217</v>
+        <v>-1.2656</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4475</v>
+        <v>-0.17</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2305</v>
+        <v>-1.0956</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.344</v>
+        <v>-1.4879</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0487</v>
+        <v>0.1615</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3927</v>
+        <v>-1.6494</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6228</v>
+        <v>-0.8208</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1758</v>
+        <v>0.4088</v>
       </c>
       <c r="L10" t="n">
-        <v>0.447</v>
+        <v>-1.2295</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9669</v>
+        <v>-0.6671</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1272</v>
+        <v>-0.2473</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8397</v>
+        <v>-0.4199</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3161</v>
+        <v>-0.965</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.8602</v>
+        <v>-1.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>0.501</v>
+        <v>0.2452</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5619</v>
+        <v>0.1249</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0608</v>
+        <v>0.1203</v>
       </c>
       <c r="V10" t="n">
         <v>0.9421</v>
       </c>
       <c r="W10" t="n">
-        <v>1.228</v>
+        <v>2.4559</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2859</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2403</v>
+        <v>-2.2135</v>
       </c>
       <c r="E11" t="n">
         <v>-2.7742</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5339</v>
+        <v>0.5607</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6995</v>
@@ -1312,13 +1312,13 @@
         <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1897</v>
+        <v>-0.1629</v>
       </c>
       <c r="T11" t="n">
         <v>-0.238</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0482</v>
+        <v>0.075</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9725</v>
+        <v>-3.8456</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.365</v>
+        <v>-2.2648</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6076</v>
+        <v>-1.5808</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9252</v>
@@ -1390,13 +1390,13 @@
         <v>1.158</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1547</v>
+        <v>-1.0278</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5949</v>
+        <v>-0.4947</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5599</v>
+        <v>-0.5331</v>
       </c>
       <c r="V12" t="n">
         <v>-2.0856</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.0772</v>
+        <v>18.0773</v>
       </c>
       <c r="E13" t="n">
-        <v>11.8723</v>
+        <v>11.8724</v>
       </c>
       <c r="F13" t="n">
-        <v>6.204800000000001</v>
+        <v>6.205</v>
       </c>
       <c r="G13" t="n">
         <v>7.142799999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>5.775500000000002</v>
+        <v>5.7755</v>
       </c>
       <c r="I13" t="n">
         <v>1.3672</v>
@@ -1444,7 +1444,7 @@
         <v>11.2425</v>
       </c>
       <c r="K13" t="n">
-        <v>9.6502</v>
+        <v>9.650199999999998</v>
       </c>
       <c r="L13" t="n">
         <v>1.5925</v>
@@ -1468,13 +1468,13 @@
         <v>13.5106</v>
       </c>
       <c r="S13" t="n">
-        <v>6.682700000000001</v>
+        <v>6.6826</v>
       </c>
       <c r="T13" t="n">
-        <v>5.1031</v>
+        <v>5.103</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5795</v>
+        <v>1.5794</v>
       </c>
       <c r="V13" t="n">
         <v>6.182100000000002</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. ARBIZU MAIZA</t>
+          <t>J. BALASTEGUI MARTINEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.141</v>
+        <v>1.5213</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7544</v>
+        <v>1.0832</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3866</v>
+        <v>0.4381</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4053</v>
+        <v>0.1896</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5859</v>
+        <v>-1.8454</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1806</v>
+        <v>2.035</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8456</v>
+        <v>1.0304</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4075</v>
+        <v>-0.2227</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5619</v>
+        <v>1.2531</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4403</v>
+        <v>-0.8409</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8216</v>
+        <v>-1.6227</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3813</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5441</v>
+        <v>1.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1943</v>
+        <v>-0.8613</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0912</v>
+        <v>-0.2102</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1032</v>
+        <v>-0.6511</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.614</v>
+        <v>1.228</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0846</v>
+        <v>1.3722</v>
       </c>
       <c r="E15" t="n">
-        <v>0.916</v>
+        <v>1.0161</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1687</v>
+        <v>0.3561</v>
       </c>
       <c r="G15" t="n">
         <v>1.5096</v>
@@ -1624,13 +1624,13 @@
         <v>1.158</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.618</v>
+        <v>-0.3305</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3424</v>
+        <v>-0.2422</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2756</v>
+        <v>-0.0883</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BALASTEGUI MARTINEZ</t>
+          <t>A. ARBIZU MAIZA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5331</v>
+        <v>0.8462</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2821</v>
+        <v>0.7544</v>
       </c>
       <c r="F16" t="n">
-        <v>0.251</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1896</v>
+        <v>0.4053</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8454</v>
+        <v>0.5859</v>
       </c>
       <c r="I16" t="n">
-        <v>2.035</v>
+        <v>-0.1806</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0304</v>
+        <v>0.8456</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2227</v>
+        <v>1.4075</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2531</v>
+        <v>-0.5619</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8409</v>
+        <v>-0.4403</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6227</v>
+        <v>-0.8216</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.3813</v>
       </c>
       <c r="P16" t="n">
-        <v>0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8494</v>
+        <v>-0.4891</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0113</v>
+        <v>-0.0912</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-0.3979</v>
       </c>
       <c r="V16" t="n">
-        <v>1.228</v>
+        <v>-0.614</v>
       </c>
       <c r="W16" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ARIZTIMUÑO MORRAS</t>
+          <t>M. BIDAURRE SOLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4997</v>
+        <v>0.8333</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9973</v>
+        <v>1.8188</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4975</v>
+        <v>-0.9856</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1181</v>
+        <v>2.6447</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7233000000000001</v>
+        <v>-2.3877</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.8414</v>
+        <v>5.0324</v>
       </c>
       <c r="J17" t="n">
-        <v>0.216</v>
+        <v>3.6326</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9572000000000001</v>
+        <v>-0.2175</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7411</v>
+        <v>3.85</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3341</v>
+        <v>-0.9878</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2338</v>
+        <v>-2.1702</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1003</v>
+        <v>1.1824</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="S17" t="n">
-        <v>2.332</v>
+        <v>-2.0044</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9116</v>
+        <v>-0.8487</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4204</v>
+        <v>-1.1558</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3281</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BIDAURRE SOLA</t>
+          <t>M. ARIZTIMUÑO MORRAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0847</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4183</v>
+        <v>0.7956</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3336</v>
+        <v>-1.6046</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6447</v>
+        <v>-1.1181</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.3877</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>5.0324</v>
+        <v>-1.8414</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6326</v>
+        <v>0.216</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2175</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>3.85</v>
+        <v>-0.7411</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9878</v>
+        <v>-1.3341</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1702</v>
+        <v>-0.2338</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1824</v>
+        <v>-1.1003</v>
       </c>
       <c r="P18" t="n">
-        <v>0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>1.158</v>
+        <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.753</v>
+        <v>1.0232</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2492</v>
+        <v>0.7099</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.5038</v>
+        <v>0.3133</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.3281</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.7997</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="19">
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7723</v>
+        <v>-0.8724</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0604</v>
+        <v>-0.1606</v>
       </c>
       <c r="F19" t="n">
         <v>-0.7119</v>
@@ -1936,10 +1936,10 @@
         <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6676</v>
+        <v>0.5675</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5037</v>
+        <v>0.4035</v>
       </c>
       <c r="U19" t="n">
         <v>0.1639</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. VICUÑA ROYO</t>
+          <t>A. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5974</v>
+        <v>-2.6165</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0596</v>
+        <v>-0.0963</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4622</v>
+        <v>-2.5202</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8868</v>
+        <v>-2.4203</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0824</v>
+        <v>-0.1997</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1956</v>
+        <v>-2.2206</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5334</v>
+        <v>-0.8191000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.6148</v>
+        <v>0.4347</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0814</v>
+        <v>-1.2538</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3534</v>
+        <v>-1.6012</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4677</v>
+        <v>-0.6344</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1142</v>
+        <v>-0.9668</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2195</v>
+        <v>-0.2191</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7549</v>
+        <v>0.151</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5354</v>
+        <v>-0.3702</v>
       </c>
       <c r="V20" t="n">
-        <v>0.614</v>
+        <v>-0.9421</v>
       </c>
       <c r="W20" t="n">
-        <v>0.614</v>
+        <v>0.5717</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GARCIA IBAÑEZ</t>
+          <t>I. VICUÑA ROYO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6499</v>
+        <v>-2.7574</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0038</v>
+        <v>-3.4602</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6537</v>
+        <v>0.7028</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4203</v>
+        <v>-1.8868</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1997</v>
+        <v>-2.0824</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2206</v>
+        <v>0.1956</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8191000000000001</v>
+        <v>-1.5334</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4347</v>
+        <v>-1.6148</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2538</v>
+        <v>0.0814</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6012</v>
+        <v>-0.3534</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6344</v>
+        <v>-0.4677</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9668</v>
+        <v>0.1142</v>
       </c>
       <c r="P21" t="n">
-        <v>0.965</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R21" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2525</v>
+        <v>0.0595</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2512</v>
+        <v>0.3543</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5037</v>
+        <v>-0.2948</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9421</v>
+        <v>0.614</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5717</v>
+        <v>0.614</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1153</v>
+        <v>-3.1896</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4501</v>
+        <v>-1.1497</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6652</v>
+        <v>-2.0399</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7171</v>
@@ -2170,13 +2170,13 @@
         <v>1.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8072</v>
+        <v>-1.8815</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3087</v>
+        <v>-1.0083</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4984</v>
+        <v>-0.8732</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5561</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8979</v>
+        <v>-3.5373</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5972</v>
+        <v>-2.3969</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3007</v>
+        <v>-1.1404</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6647999999999999</v>
@@ -2248,13 +2248,13 @@
         <v>1.158</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9472</v>
+        <v>-0.5866</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5949</v>
+        <v>-0.3946</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3523</v>
+        <v>-0.192</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5138</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.387700000000001</v>
+        <v>-8.2003</v>
       </c>
       <c r="E24" t="n">
         <v>-4.4095</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.9782</v>
+        <v>-3.7908</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8728</v>
@@ -2326,13 +2326,13 @@
         <v>1.9301</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4799</v>
+        <v>-1.2925</v>
       </c>
       <c r="T24" t="n">
         <v>-0.4032</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0768</v>
+        <v>-0.8894</v>
       </c>
       <c r="V24" t="n">
         <v>-3.0699</v>
@@ -2359,31 +2359,31 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-18.0774</v>
+        <v>-17.4095</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.2049</v>
+        <v>-6.205100000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.8723</v>
+        <v>-11.2046</v>
       </c>
       <c r="G25" t="n">
         <v>-7.1426</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.775300000000001</v>
+        <v>-5.775299999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.3672</v>
+        <v>-1.367200000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>4.0999</v>
+        <v>4.099899999999999</v>
       </c>
       <c r="K25" t="n">
         <v>3.8748</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2251000000000005</v>
+        <v>0.2251000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-11.2424</v>
@@ -2404,13 +2404,13 @@
         <v>15.4406</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.6824</v>
+        <v>-6.014799999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.5795</v>
+        <v>-1.5797</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.1031</v>
+        <v>-4.4355</v>
       </c>
       <c r="V25" t="n">
         <v>-6.182</v>
